--- a/main/StructureDefinition-bc-metadata-parameters-subscription.xlsx
+++ b/main/StructureDefinition-bc-metadata-parameters-subscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,7 +351,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -2481,7 +2481,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>157</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>162</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>163</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>166</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>171</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>176</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>180</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>185</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>186</v>
       </c>
@@ -5167,12 +5167,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL39">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
